--- a/data/trans_camb/IP16B01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,96; 94,73</t>
+          <t>58,8; 94,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,81; 100,0</t>
+          <t>52,67; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,39; 100,0</t>
+          <t>62,55; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,47; 100,0</t>
+          <t>53,64; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,65; 92,64</t>
+          <t>65,5; 92,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,08; 95,57</t>
+          <t>64,97; 95,46</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,96; 90,53</t>
+          <t>74,08; 90,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,61; 87,0</t>
+          <t>67,16; 86,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,14; 99,01</t>
+          <t>89,69; 98,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,59; 95,21</t>
+          <t>79,59; 95,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,22; 93,85</t>
+          <t>84,51; 93,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,22; 89,28</t>
+          <t>76,32; 88,8</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,58; 88,21</t>
+          <t>60,58; 88,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65,59; 96,15</t>
+          <t>65,83; 95,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,92; 97,31</t>
+          <t>77,58; 97,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,54; 95,56</t>
+          <t>63,62; 95,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,36; 91,52</t>
+          <t>73,05; 91,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,65; 94,2</t>
+          <t>72,57; 93,56</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>74,24; 86,95</t>
+          <t>74,06; 87,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>72,36; 87,82</t>
+          <t>72,17; 87,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,99</t>
+          <t>88,05; 97,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81,16; 93,98</t>
+          <t>80,09; 93,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,16; 90,79</t>
+          <t>82,86; 90,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,38; 88,8</t>
+          <t>78,49; 88,55</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2147,22; —</t>
+          <t>2177,73; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2188,07; —</t>
+          <t>2006,35; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5550,15; —</t>
+          <t>4355,1; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5296,26; —</t>
+          <t>5006,02; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,8; 94,77</t>
+          <t>59,18; 95,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,67; 100,0</t>
+          <t>49,7; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,55; 100,0</t>
+          <t>64,85; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,64; 100,0</t>
+          <t>53,72; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,5; 92,6</t>
+          <t>67,45; 94,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,97; 95,46</t>
+          <t>64,9; 95,75</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,08; 90,31</t>
+          <t>74,69; 90,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,16; 86,77</t>
+          <t>66,01; 86,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,69; 98,95</t>
+          <t>89,09; 98,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,59; 95,43</t>
+          <t>78,85; 95,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,51; 93,44</t>
+          <t>84,59; 93,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,32; 88,8</t>
+          <t>76,56; 89,56</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,58; 88,86</t>
+          <t>58,62; 88,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65,83; 95,96</t>
+          <t>66,18; 96,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,58; 97,38</t>
+          <t>75,41; 97,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,62; 95,52</t>
+          <t>60,98; 95,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,05; 91,12</t>
+          <t>74,63; 91,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,57; 93,56</t>
+          <t>72,93; 93,43</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>74,06; 87,17</t>
+          <t>73,61; 87,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>72,17; 87,06</t>
+          <t>72,02; 86,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,03</t>
+          <t>87,96; 96,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,09; 93,75</t>
+          <t>80,18; 93,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,86; 90,75</t>
+          <t>83,24; 90,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,49; 88,55</t>
+          <t>79,12; 88,67</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2177,73; —</t>
+          <t>2357,06; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2006,35; —</t>
+          <t>2324,28; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4355,1; —</t>
+          <t>5608,98; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5006,02; —</t>
+          <t>5050,88; —</t>
         </is>
       </c>
     </row>
